--- a/LISTAS_ORDENADAS/MA/Tornillos Pitones Arandelas Tuercas/TUERCAS dismay.xlsx
+++ b/LISTAS_ORDENADAS/MA/Tornillos Pitones Arandelas Tuercas/TUERCAS dismay.xlsx
@@ -780,15 +780,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="23" t="n">
-        <v>45211.54080906303</v>
+        <v>45266</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="21" t="n"/>
     </row>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="24">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -804,7 +801,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
     </row>
@@ -833,19 +830,10 @@
     <row r="11" ht="41.25" customHeight="1" s="24">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
+          <t>    </t>
+        </is>
+      </c>
+    </row>
     <row r="21" ht="18" customHeight="1" s="24">
       <c r="E21" s="6" t="n"/>
     </row>
@@ -883,7 +871,7 @@
         </is>
       </c>
       <c r="D23" s="16" t="n">
-        <v>5332.9</v>
+        <v>4848.095</v>
       </c>
       <c r="E23" s="6" t="n"/>
     </row>
@@ -902,7 +890,7 @@
         </is>
       </c>
       <c r="D24" s="16" t="n">
-        <v>7351.33</v>
+        <v>6683.032</v>
       </c>
       <c r="E24" s="6" t="n"/>
     </row>
@@ -921,7 +909,7 @@
         </is>
       </c>
       <c r="D25" s="16" t="n">
-        <v>10453.34</v>
+        <v>9503.041999999999</v>
       </c>
       <c r="E25" s="6" t="n"/>
     </row>
@@ -940,7 +928,7 @@
         </is>
       </c>
       <c r="D26" s="16" t="n">
-        <v>15595.03</v>
+        <v>14177.304</v>
       </c>
       <c r="E26" s="6" t="n"/>
     </row>
@@ -959,7 +947,7 @@
         </is>
       </c>
       <c r="D27" s="16" t="n">
-        <v>28130.54</v>
+        <v>25573.226</v>
       </c>
       <c r="E27" s="6" t="n"/>
     </row>
@@ -978,7 +966,7 @@
         </is>
       </c>
       <c r="D28" s="16" t="n">
-        <v>36416.73</v>
+        <v>33106.119</v>
       </c>
       <c r="E28" s="6" t="n"/>
     </row>
@@ -1029,7 +1017,6 @@
         </is>
       </c>
     </row>
-    <row r="34"/>
     <row r="35" ht="18" customHeight="1" s="24">
       <c r="A35" s="17" t="inlineStr">
         <is>
@@ -1084,7 +1071,6 @@
         <v>4696</v>
       </c>
     </row>
-    <row r="38"/>
     <row r="39" ht="15.75" customHeight="1" s="24">
       <c r="A39" s="11" t="inlineStr">
         <is>
@@ -1099,8 +1085,6 @@
         </is>
       </c>
     </row>
-    <row r="41"/>
-    <row r="42"/>
     <row r="43" ht="15.75" customHeight="1" s="24">
       <c r="A43" s="19" t="n"/>
     </row>
